--- a/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
+++ b/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.037</v>
+        <v>-0.027</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.027</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.017</v>
+        <v>0.013</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.022</v>
+        <v>-0.012</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.012</v>
+        <v>0.008</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.028</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.008</v>
+        <v>0.048</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.018</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.052</v>
+        <v>-0.042</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.042</v>
+        <v>-0.022</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.032</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.022</v>
+        <v>0.018</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.012</v>
+        <v>0.03800000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
@@ -3727,27 +3727,27 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6x</t>
+          <t>12x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>16x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>12x</t>
+          <t>18x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>14x</t>
+          <t>20x</t>
         </is>
       </c>
     </row>
@@ -3756,23 +3756,23 @@
         <v>0.0541</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*6/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*18/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*20/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3781,23 +3781,23 @@
         <v>0.06409999999999999</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*6/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*18/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*20/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3806,23 +3806,23 @@
         <v>0.0741</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*6/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*18/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*20/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3831,23 +3831,23 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*6/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*18/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*20/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3856,23 +3856,23 @@
         <v>0.09409999999999999</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*6/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*18/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*20/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3881,23 +3881,23 @@
         <v>0.1041</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*6/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*18/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*20/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3906,23 +3906,23 @@
         <v>0.1141</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*6/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*18/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*20/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
+++ b/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>-0.027</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="6" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="J8" s="6" t="n">
         <v>-0.006999999999999999</v>
       </c>
-      <c r="I8" s="6" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0.033</v>
-      </c>
       <c r="K8" s="6" t="n">
-        <v>0.05</v>
+        <v>0.003000000000000003</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>-0.012</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="6" t="n">
+        <v>-0.002000000000000002</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>0.008</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0.048</v>
-      </c>
       <c r="K9" s="6" t="n">
-        <v>0.05</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>-0.042</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="6" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>-0.022</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>-0.002000000000000002</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.018</v>
-      </c>
       <c r="K10" s="6" t="n">
-        <v>0.03800000000000001</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="11">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -3727,27 +3727,27 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
+          <t>6x</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>8x</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
           <t>12x</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>14x</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>16x</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>18x</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>20x</t>
         </is>
       </c>
     </row>
@@ -3756,23 +3756,23 @@
         <v>0.0541</v>
       </c>
       <c r="C39" s="22">
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*6/(1+$A$39)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="D39" s="22">
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="E39" s="22">
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="F39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
-      <c r="D39" s="22">
+      <c r="G39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*16/(1+$A$39)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*18/(1+$A$39)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*20/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3781,23 +3781,23 @@
         <v>0.06409999999999999</v>
       </c>
       <c r="C40" s="22">
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*6/(1+$A$40)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="D40" s="22">
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="E40" s="22">
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="F40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
-      <c r="D40" s="22">
+      <c r="G40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*16/(1+$A$40)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*18/(1+$A$40)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*20/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3806,23 +3806,23 @@
         <v>0.0741</v>
       </c>
       <c r="C41" s="22">
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*6/(1+$A$41)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="D41" s="22">
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="E41" s="22">
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="F41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
-      <c r="D41" s="22">
+      <c r="G41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*16/(1+$A$41)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*18/(1+$A$41)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*20/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3831,23 +3831,23 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="C42" s="22">
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*6/(1+$A$42)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="D42" s="22">
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="F42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
-      <c r="D42" s="22">
+      <c r="G42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*16/(1+$A$42)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*18/(1+$A$42)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*20/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3856,23 +3856,23 @@
         <v>0.09409999999999999</v>
       </c>
       <c r="C43" s="22">
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*6/(1+$A$43)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="D43" s="22">
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="E43" s="22">
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="F43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
-      <c r="D43" s="22">
+      <c r="G43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*16/(1+$A$43)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*18/(1+$A$43)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*20/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3881,23 +3881,23 @@
         <v>0.1041</v>
       </c>
       <c r="C44" s="22">
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*6/(1+$A$44)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="D44" s="22">
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="E44" s="22">
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="F44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
-      <c r="D44" s="22">
+      <c r="G44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*16/(1+$A$44)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*18/(1+$A$44)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*20/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
@@ -3906,23 +3906,23 @@
         <v>0.1141</v>
       </c>
       <c r="C45" s="22">
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*6/(1+$A$45)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="D45" s="22">
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="E45" s="22">
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <v/>
+      </c>
+      <c r="F45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
-      <c r="D45" s="22">
+      <c r="G45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*16/(1+$A$45)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*18/(1+$A$45)^5+$C$29)/$C$32</f>
-        <v/>
-      </c>
-      <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*20/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
+++ b/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.037</v>
+        <v>-0.027</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.027</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.017</v>
+        <v>0.013</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.022</v>
+        <v>-0.012</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.012</v>
+        <v>0.008</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.028</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.008</v>
+        <v>0.048</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.018</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.052</v>
+        <v>-0.042</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.042</v>
+        <v>-0.022</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.032</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.022</v>
+        <v>0.018</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.012</v>
+        <v>0.03800000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.3564039678365152</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.3514039678365152</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.3614039678365152</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.06953831239270093</v>
+        <v>0.06487168615999957</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.06953831239270093</v>
+        <v>0.06487168615999957</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.06953831239270093</v>
+        <v>0.06487168615999957</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.06953831239270093</v>
+        <v>0.06487168615999957</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.06953831239270093</v>
+        <v>0.06487168615999957</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0796</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0741</v>
+        <v>0.06960000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.09409999999999999</v>
+        <v>0.0896</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>457.95</v>
+        <v>455.75</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/457.95-1</f>
+        <f>C33/455.75-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6x</t>
+          <t>12x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>16x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>12x</t>
+          <t>18x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>14x</t>
+          <t>20x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0541</v>
+        <v>0.04960000000000001</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*6/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*18/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*20/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.06409999999999999</v>
+        <v>0.0596</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*6/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*18/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*20/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0741</v>
+        <v>0.06960000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*6/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*18/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*20/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0796</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*6/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*18/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*20/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.09409999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*6/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*18/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*20/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1041</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*6/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*18/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*20/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1141</v>
+        <v>0.1096</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*6/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*18/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*20/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
+++ b/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
@@ -519,7 +519,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC.PA) - Assumptions</t>
+          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC_PA) - Assumptions</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.3564039678365152</v>
+        <v>0.4314088187393741</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.3514039678365152</v>
+        <v>0.4264088187393741</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.3614039678365152</v>
+        <v>0.4364088187393741</v>
       </c>
     </row>
     <row r="23">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0796</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.06960000000000001</v>
+        <v>0.07200000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.0896</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="38">
@@ -1243,7 +1243,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC.PA) - Historical Financial Statements</t>
+          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC_PA) - Historical Financial Statements</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1529,10 +1529,10 @@
         <v>26721</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>29776</v>
+        <v>29777</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>27095</v>
+        <v>27094</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>25850</v>
@@ -1548,10 +1548,10 @@
         <v>0.3374587979743127</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.3456176801736446</v>
+        <v>0.3456292874305015</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.3199617392125835</v>
+        <v>0.3199499303275785</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>0.319898028636133</v>
@@ -1658,7 +1658,7 @@
         <v>42695</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>45895</v>
+        <v>46506</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>44018</v>
@@ -1935,7 +1935,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC.PA) - Financial Model</t>
+          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC_PA) - Financial Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3255,7 +3255,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC.PA) - DCF Valuation</t>
+          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC_PA) - DCF Valuation</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>455.75</v>
+        <v>471.05</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/455.75-1</f>
+        <f>C33/471.05-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.04960000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0596</v>
+        <v>0.062</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.06960000000000001</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0796</v>
+        <v>0.082</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.0896</v>
+        <v>0.092</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1096</v>
+        <v>0.112</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>

--- a/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
+++ b/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.027</v>
+        <v>-0.02</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.013</v>
+        <v>0.05</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.033</v>
+        <v>0.05</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="9">
@@ -660,16 +660,16 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.012</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.008</v>
+        <v>0.06</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.028</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.048</v>
+        <v>0.06</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0.05</v>
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.042</v>
+        <v>-0.04</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.022</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.02</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.03800000000000001</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6763019964726482</v>
+        <v>0.67</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.6763019964726482</v>
+        <v>0.67</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.6763019964726482</v>
+        <v>0.67</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.6763019964726482</v>
+        <v>0.67</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.6763019964726482</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.6863019964726482</v>
+        <v>0.68</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.6863019964726482</v>
+        <v>0.68</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6863019964726482</v>
+        <v>0.68</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.6863019964726482</v>
+        <v>0.68</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.6863019964726482</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.6663019964726482</v>
+        <v>0.66</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6663019964726482</v>
+        <v>0.66</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6663019964726482</v>
+        <v>0.66</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.6663019964726482</v>
+        <v>0.66</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.6663019964726482</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.43</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.43</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.43</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.43</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.4314088187393741</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.42</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.42</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.42</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.42</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.4264088187393741</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.44</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.44</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.44</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.44</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.4364088187393741</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="23">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.08825225940030977</v>
+        <v>0.09</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.08825225940030977</v>
+        <v>0.09</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.08825225940030977</v>
+        <v>0.09</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.08825225940030977</v>
+        <v>0.09</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.08825225940030977</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="31">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.06487168615999957</v>
+        <v>0.065</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.06487168615999957</v>
+        <v>0.065</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.06487168615999957</v>
+        <v>0.065</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.06487168615999957</v>
+        <v>0.065</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.06487168615999957</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="32">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.2693866919386977</v>
+        <v>0.27</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.2693866919386977</v>
+        <v>0.27</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.2693866919386977</v>
+        <v>0.27</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.2693866919386977</v>
+        <v>0.27</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.2693866919386977</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="34">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.082</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.092</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -1529,7 +1529,7 @@
         <v>26721</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>29777</v>
+        <v>29776</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>27094</v>
@@ -1548,7 +1548,7 @@
         <v>0.3374587979743127</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.3456292874305015</v>
+        <v>0.3456176801736446</v>
       </c>
       <c r="E22" s="11" t="n">
         <v>0.3199499303275785</v>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>471.05</v>
+        <v>490.55</v>
       </c>
     </row>
     <row r="4">
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>495.867312</v>
+        <v>494.271227</v>
       </c>
     </row>
     <row r="33">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/471.05-1</f>
+        <f>C33/490.55-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>12x</t>
+          <t>9x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>14x</t>
+          <t>11x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>16x</t>
+          <t>13x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>18x</t>
+          <t>15x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>20x</t>
+          <t>17x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.052</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*18/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*20/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*17/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.062</v>
+        <v>0.08</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*18/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*20/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*17/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*18/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*20/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*17/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.082</v>
+        <v>0.1</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*18/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*20/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*17/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.092</v>
+        <v>0.11</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*18/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*20/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*17/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.102</v>
+        <v>0.12</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*18/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*20/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*17/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.112</v>
+        <v>0.13</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*18/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*20/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*17/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
+++ b/data/valuations/MC_PA/MC_PA_modelo_valoracion.xlsx
@@ -519,7 +519,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC_PA) - Assumptions</t>
+          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC.PA) - Assumptions</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H9" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>0.06</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0</v>
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.68</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.66</v>
+        <v>0.675</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.66</v>
+        <v>0.675</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.66</v>
+        <v>0.675</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.66</v>
+        <v>0.675</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.66</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="23">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.09</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.095</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -1243,7 +1243,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC_PA) - Historical Financial Statements</t>
+          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC.PA) - Historical Financial Statements</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1935,7 +1935,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC_PA) - Financial Model</t>
+          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC.PA) - Financial Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3255,7 +3255,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC_PA) - DCF Valuation</t>
+          <t>LVMH Moët Hennessy - Louis Vuitton, Société Européenne (MC.PA) - DCF Valuation</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>490.55</v>
+        <v>456.25</v>
       </c>
     </row>
     <row r="4">
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>494.271227</v>
+        <v>494.077227</v>
       </c>
     </row>
     <row r="33">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/490.55-1</f>
+        <f>C33/456.25-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.08</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.11</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9/(1+$A$45)^5+$C$29)/$C$32</f>
